--- a/Ohio_State_2025-26_ncaam_stats.xlsx
+++ b/Ohio_State_2025-26_ncaam_stats.xlsx
@@ -15,7 +15,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avg Assists" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avg Rebounds" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avg 3PM" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Points" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8829,717 +8828,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Game Time (PST)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Opponent</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Team Points</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Opponent Points</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Game Total Points</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>80</v>
-      </c>
-      <c r="D2" t="n">
-        <v>72</v>
-      </c>
-      <c r="E2" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Youngstown State</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>81</v>
-      </c>
-      <c r="D3" t="n">
-        <v>47</v>
-      </c>
-      <c r="E3" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>64</v>
-      </c>
-      <c r="D4" t="n">
-        <v>78</v>
-      </c>
-      <c r="E4" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Evansville</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>80</v>
-      </c>
-      <c r="D5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Campbell</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>104</v>
-      </c>
-      <c r="D6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E6" t="n">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Green Bay</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>102</v>
-      </c>
-      <c r="D7" t="n">
-        <v>69</v>
-      </c>
-      <c r="E7" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Pittsburgh</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>90</v>
-      </c>
-      <c r="D8" t="n">
-        <v>91</v>
-      </c>
-      <c r="E8" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Maryland</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>59</v>
-      </c>
-      <c r="D9" t="n">
-        <v>83</v>
-      </c>
-      <c r="E9" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2024-12-07</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rutgers</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>80</v>
-      </c>
-      <c r="D10" t="n">
-        <v>66</v>
-      </c>
-      <c r="E10" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2024-12-14</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Auburn</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>53</v>
-      </c>
-      <c r="D11" t="n">
-        <v>91</v>
-      </c>
-      <c r="E11" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Valparaiso</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>95</v>
-      </c>
-      <c r="D12" t="n">
-        <v>73</v>
-      </c>
-      <c r="E12" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2024-12-21</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Kentucky</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>85</v>
-      </c>
-      <c r="D13" t="n">
-        <v>65</v>
-      </c>
-      <c r="E13" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Indiana State</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>103</v>
-      </c>
-      <c r="D14" t="n">
-        <v>83</v>
-      </c>
-      <c r="E14" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Michigan State</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>62</v>
-      </c>
-      <c r="D15" t="n">
-        <v>69</v>
-      </c>
-      <c r="E15" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2025-01-07</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Minnesota</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>89</v>
-      </c>
-      <c r="D16" t="n">
-        <v>88</v>
-      </c>
-      <c r="E16" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025-01-09</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>71</v>
-      </c>
-      <c r="D17" t="n">
-        <v>73</v>
-      </c>
-      <c r="E17" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>68</v>
-      </c>
-      <c r="D18" t="n">
-        <v>70</v>
-      </c>
-      <c r="E18" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Indiana</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>76</v>
-      </c>
-      <c r="D19" t="n">
-        <v>77</v>
-      </c>
-      <c r="E19" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Purdue</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>73</v>
-      </c>
-      <c r="D20" t="n">
-        <v>70</v>
-      </c>
-      <c r="E20" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Iowa</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>82</v>
-      </c>
-      <c r="D21" t="n">
-        <v>65</v>
-      </c>
-      <c r="E21" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Penn State</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>83</v>
-      </c>
-      <c r="D22" t="n">
-        <v>64</v>
-      </c>
-      <c r="E22" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Illinois</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>79</v>
-      </c>
-      <c r="D23" t="n">
-        <v>87</v>
-      </c>
-      <c r="E23" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2025-02-07</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Maryland</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>73</v>
-      </c>
-      <c r="D24" t="n">
-        <v>70</v>
-      </c>
-      <c r="E24" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2025-02-09</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Nebraska</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>71</v>
-      </c>
-      <c r="D25" t="n">
-        <v>79</v>
-      </c>
-      <c r="E25" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>93</v>
-      </c>
-      <c r="D26" t="n">
-        <v>69</v>
-      </c>
-      <c r="E26" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Michigan</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>83</v>
-      </c>
-      <c r="D27" t="n">
-        <v>86</v>
-      </c>
-      <c r="E27" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2025-02-20</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Northwestern</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>49</v>
-      </c>
-      <c r="D28" t="n">
-        <v>70</v>
-      </c>
-      <c r="E28" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>UCLA</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>61</v>
-      </c>
-      <c r="D29" t="n">
-        <v>69</v>
-      </c>
-      <c r="E29" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>USC</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>87</v>
-      </c>
-      <c r="D30" t="n">
-        <v>82</v>
-      </c>
-      <c r="E30" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Nebraska</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>116</v>
-      </c>
-      <c r="D31" t="n">
-        <v>114</v>
-      </c>
-      <c r="E31" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Indiana</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>60</v>
-      </c>
-      <c r="D32" t="n">
-        <v>66</v>
-      </c>
-      <c r="E32" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Iowa</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>70</v>
-      </c>
-      <c r="D33" t="n">
-        <v>77</v>
-      </c>
-      <c r="E33" t="n">
-        <v>147</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>